--- a/最後通牒結果/高主体感のみ箱ひげ図.xlsx
+++ b/最後通牒結果/高主体感のみ箱ひげ図.xlsx
@@ -8,34 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amazo/Documents/修論/実験結果/最後通牒結果/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61E0D35F-4909-5E49-B77F-2D1FA628EAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FCEF27-E3BC-C44A-B7D7-A0FA99B2F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9940" yWindow="1900" windowWidth="28300" windowHeight="17360" xr2:uid="{555EC506-CD65-B14B-AB35-5675DA7CD187}"/>
+    <workbookView xWindow="5280" yWindow="1400" windowWidth="17460" windowHeight="17360" xr2:uid="{555EC506-CD65-B14B-AB35-5675DA7CD187}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$E$2</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$A$3:$E$3</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$A$2:$E$2</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$A$3:$E$3</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$A$4:$E$4</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$A$5:$E$5</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$A$6:$E$6</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$B$2:$B$6</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$D$2:$D$6</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$E$2:$E$6</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$4:$E$4</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$A$5:$E$5</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$6:$E$6</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$I$2:$M$2</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$I$3:$M$3</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$I$4:$M$4</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$I$5:$M$5</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$I$6:$M$6</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$A$2:$E$2</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$A$3:$E$3</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$4:$E$4</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$A$5:$E$5</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$A$6:$E$6</definedName>
-    <definedName name="高主体感群_箱ひげ図用_1" localSheetId="0">Sheet1!$A$1:$K$6</definedName>
+    <definedName name="高主体感群_箱ひげ図用_1" localSheetId="0">Sheet1!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -165,6 +158,732 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f dir="row">_xlchart.v1.0</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f dir="row">_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f dir="row">_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f dir="row">_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="4">
+      <cx:numDim type="val">
+        <cx:f dir="row">_xlchart.v1.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{D08F5853-934C-944B-8862-CC84ACEE3F7B}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{517028BA-9073-D64F-87F4-6CE1B3C7D5F4}">
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{46BFC82A-AB7A-704B-892D-A02A4EC87283}">
+          <cx:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </cx:spPr>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{1F3DEE77-B344-8B41-9C44-F27DBDCB6D4F}">
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{E29FFCE9-F693-2642-B3FB-D67D4D3C61BC}">
+          <cx:dataId val="4"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>435901</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>76994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>645410</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>55298</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="グラフ 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0BC3451-0859-EE60-6D9A-CED3E7AA8F3E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12424701" y="2108994"/>
+              <a:ext cx="4019509" cy="2772304"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>この図は、お使いのバージョンの Excel では利用できません。
+この図形を編集するか、このブックを異なるファイル形式に保存すると、グラフが恒久的に壊れます。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,13 +1207,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73A7E4C-A1EB-2B40-AAFC-1809F4382147}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,20 +1226,20 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>60</v>
       </c>
@@ -533,20 +1252,20 @@
       <c r="E2">
         <v>45</v>
       </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>50</v>
       </c>
       <c r="J2">
         <v>50</v>
       </c>
-      <c r="K2">
+      <c r="L2">
+        <v>50</v>
+      </c>
+      <c r="M2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>45</v>
       </c>
@@ -559,20 +1278,20 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
+        <v>50</v>
+      </c>
+      <c r="J3">
         <v>70</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>60</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>45</v>
       </c>
@@ -585,20 +1304,20 @@
       <c r="E4">
         <v>75</v>
       </c>
-      <c r="G4">
-        <v>50</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>50</v>
       </c>
       <c r="J4">
         <v>50</v>
       </c>
-      <c r="K4">
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>60</v>
       </c>
@@ -611,20 +1330,20 @@
       <c r="E5">
         <v>50</v>
       </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>50</v>
       </c>
       <c r="J5">
+        <v>50</v>
+      </c>
+      <c r="L5">
         <v>60</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>50</v>
       </c>
@@ -637,21 +1356,22 @@
       <c r="E6">
         <v>30</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>55</v>
       </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
       <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="L6">
         <v>60</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/最後通牒結果/高主体感のみ箱ひげ図.xlsx
+++ b/最後通牒結果/高主体感のみ箱ひげ図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amazo/Documents/修論/実験結果/最後通牒結果/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FCEF27-E3BC-C44A-B7D7-A0FA99B2F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491D8DCA-3439-9B49-8EFA-514E6FD1C1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1400" windowWidth="17460" windowHeight="17360" xr2:uid="{555EC506-CD65-B14B-AB35-5675DA7CD187}"/>
   </bookViews>
@@ -16,19 +16,36 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$I$2:$M$2</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$I$3:$M$3</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$I$4:$M$4</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$I$5:$M$5</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$I$6:$M$6</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$A$2:$E$2</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$A$3:$E$3</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$4:$E$4</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$A$5:$E$5</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$A$6:$E$6</definedName>
-    <definedName name="高主体感群_箱ひげ図用_1" localSheetId="0">Sheet1!$A$1:$M$6</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$I$2:$I$6</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$J$2:$J$6</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$I$4:$L$4</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$I$5:$L$5</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$I$6:$L$6</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$A$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$B$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$B$2:$B$6</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$C$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$C$2:$C$6</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$K$2:$K$6</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$D$2:$D$6</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$I$2:$I$6</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$J$2:$J$6</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$K$2:$K$6</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$L$2:$L$6</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$I$2:$I$6</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$J$2:$J$6</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$K$2:$K$6</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Sheet1!$L$2:$L$6</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$L$2:$L$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$I$2:$I$6</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$J$2:$J$6</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$K$2:$K$6</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$L$2:$L$6</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$I$2:$L$2</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$I$3:$L$3</definedName>
+    <definedName name="高主体感群_箱ひげ図用_1" localSheetId="0">Sheet1!$A$1:$L$6</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -165,69 +182,75 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.16</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.18</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.3</cx:f>
-      </cx:numDim>
-    </cx:data>
-    <cx:data id="4">
-      <cx:numDim type="val">
-        <cx:f dir="row">_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.20</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{D08F5853-934C-944B-8862-CC84ACEE3F7B}">
+        <cx:series layoutId="boxWhisker" uniqueId="{D2FF74FA-4883-6041-BAAC-0B84E5A676A2}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.13</cx:f>
+              <cx:v>男性→男性 VCあり</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{517028BA-9073-D64F-87F4-6CE1B3C7D5F4}">
+        <cx:series layoutId="boxWhisker" uniqueId="{8C0628A7-300E-DF4E-9119-7CF08B2DA120}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.15</cx:f>
+              <cx:v>男性→男性 VCなし</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="1"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{46BFC82A-AB7A-704B-892D-A02A4EC87283}">
-          <cx:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </cx:spPr>
+        <cx:series layoutId="boxWhisker" uniqueId="{E40D586F-2DB3-0444-BDC2-547F2C2F63B3}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.17</cx:f>
+              <cx:v>男性→女性 VCあり</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="2"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{1F3DEE77-B344-8B41-9C44-F27DBDCB6D4F}">
+        <cx:series layoutId="boxWhisker" uniqueId="{B66CB088-D8A9-6C4B-8D76-D28A72D9DFE4}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.19</cx:f>
+              <cx:v>男性→女性 VCなし</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="3"/>
-          <cx:layoutPr>
-            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
-            <cx:statistics quartileMethod="exclusive"/>
-          </cx:layoutPr>
-        </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{E29FFCE9-F693-2642-B3FB-D67D4D3C61BC}">
-          <cx:dataId val="4"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
             <cx:statistics quartileMethod="exclusive"/>
@@ -239,7 +262,77 @@
         <cx:tickLabels/>
       </cx:axis>
       <cx:axis id="1">
-        <cx:valScaling/>
+        <cx:valScaling min="20"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.25</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.26</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.27</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.28</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{B5B9CD2A-558C-BA4C-8E69-BEAF71E52BF9}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{B98BFA29-EC9A-9746-B0CE-F75507930E54}">
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{05EE706E-030C-914D-87A1-44CA9721A7CE}">
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{EA649197-BD02-B746-B6C7-8533F950BEEF}">
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="100" min="20"/>
         <cx:majorGridlines/>
         <cx:tickLabels/>
       </cx:axis>
@@ -288,6 +381,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
   <cs:axisTitle>
@@ -803,29 +936,544 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>435901</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76994</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>567267</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>645410</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>55298</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>618067</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>33867</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="グラフ 1">
+            <xdr:cNvPr id="3" name="グラフ 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0BC3451-0859-EE60-6D9A-CED3E7AA8F3E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC623E8-1ADF-BCE0-0734-2C2BCAA1597B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -852,8 +1500,86 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12424701" y="2108994"/>
-              <a:ext cx="4019509" cy="2772304"/>
+              <a:off x="567267" y="2624667"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="ja-JP" altLang="en-US" sz="1100"/>
+                <a:t>この図は、お使いのバージョンの Excel では利用できません。
+この図形を編集するか、このブックを異なるファイル形式に保存すると、グラフが恒久的に壊れます。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>880533</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="グラフ 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E5DC217-D08B-00A2-075F-9F39341B419A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11430000" y="3708400"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1207,23 +1933,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73A7E4C-A1EB-2B40-AAFC-1809F4382147}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="I1" t="s">
@@ -1232,24 +1958,24 @@
       <c r="J1" t="s">
         <v>5</v>
       </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
       <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>60</v>
       </c>
       <c r="B2">
         <v>60</v>
       </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
       <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
         <v>45</v>
       </c>
       <c r="I2">
@@ -1258,50 +1984,50 @@
       <c r="J2">
         <v>50</v>
       </c>
+      <c r="K2">
+        <v>50</v>
+      </c>
       <c r="L2">
         <v>50</v>
       </c>
-      <c r="M2">
-        <v>50</v>
-      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>45</v>
       </c>
       <c r="B3">
         <v>50</v>
       </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
       <c r="D3">
         <v>50</v>
       </c>
-      <c r="E3">
-        <v>50</v>
-      </c>
       <c r="I3">
         <v>50</v>
       </c>
       <c r="J3">
         <v>70</v>
       </c>
+      <c r="K3">
+        <v>60</v>
+      </c>
       <c r="L3">
-        <v>60</v>
-      </c>
-      <c r="M3">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>45</v>
       </c>
       <c r="B4">
         <v>75</v>
       </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
       <c r="D4">
-        <v>90</v>
-      </c>
-      <c r="E4">
         <v>75</v>
       </c>
       <c r="I4">
@@ -1310,24 +2036,24 @@
       <c r="J4">
         <v>50</v>
       </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
       <c r="L4">
         <v>50</v>
       </c>
-      <c r="M4">
-        <v>50</v>
-      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>60</v>
       </c>
       <c r="B5">
         <v>60</v>
       </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
       <c r="D5">
-        <v>60</v>
-      </c>
-      <c r="E5">
         <v>50</v>
       </c>
       <c r="I5">
@@ -1336,24 +2062,24 @@
       <c r="J5">
         <v>50</v>
       </c>
+      <c r="K5">
+        <v>60</v>
+      </c>
       <c r="L5">
-        <v>60</v>
-      </c>
-      <c r="M5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>50</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
+      <c r="C6">
+        <v>80</v>
+      </c>
       <c r="D6">
-        <v>80</v>
-      </c>
-      <c r="E6">
         <v>30</v>
       </c>
       <c r="I6">
@@ -1362,10 +2088,10 @@
       <c r="J6">
         <v>50</v>
       </c>
+      <c r="K6">
+        <v>60</v>
+      </c>
       <c r="L6">
-        <v>60</v>
-      </c>
-      <c r="M6">
         <v>55</v>
       </c>
     </row>
